--- a/data/health/Life expectancy inequalities in the South West/Life expectancy inequality at birth in the South West and England, 2011 - 13 to 2022 - 24.xlsx
+++ b/data/health/Life expectancy inequalities in the South West/Life expectancy inequality at birth in the South West and England, 2011 - 13 to 2022 - 24.xlsx
@@ -10091,7 +10091,7 @@
       <c r="AI2" s="2" t="inlineStr"/>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -10213,7 +10213,7 @@
       <c r="AI3" s="2" t="inlineStr"/>
       <c r="AJ3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -10339,7 +10339,7 @@
       <c r="AI4" s="2" t="inlineStr"/>
       <c r="AJ4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -10461,7 +10461,7 @@
       <c r="AI5" s="2" t="inlineStr"/>
       <c r="AJ5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10587,7 @@
       <c r="AI6" s="2" t="inlineStr"/>
       <c r="AJ6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -10709,7 +10709,7 @@
       <c r="AI7" s="2" t="inlineStr"/>
       <c r="AJ7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -10835,7 +10835,7 @@
       <c r="AI8" s="2" t="inlineStr"/>
       <c r="AJ8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -10957,7 +10957,7 @@
       <c r="AI9" s="2" t="inlineStr"/>
       <c r="AJ9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -11083,7 +11083,7 @@
       <c r="AI10" s="2" t="inlineStr"/>
       <c r="AJ10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11205,7 @@
       <c r="AI11" s="2" t="inlineStr"/>
       <c r="AJ11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -11331,7 +11331,7 @@
       <c r="AI12" s="2" t="inlineStr"/>
       <c r="AJ12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -11453,7 +11453,7 @@
       <c r="AI13" s="2" t="inlineStr"/>
       <c r="AJ13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -11489,7 +11489,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
       <c r="AI14" s="2" t="inlineStr"/>
       <c r="AJ14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -11615,7 +11615,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
       <c r="AI15" s="2" t="inlineStr"/>
       <c r="AJ15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
       <c r="AI16" s="2" t="inlineStr"/>
       <c r="AJ16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -11863,7 +11863,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
       <c r="AI17" s="2" t="inlineStr"/>
       <c r="AJ17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -11985,7 +11985,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
       <c r="AI18" s="2" t="inlineStr"/>
       <c r="AJ18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -12111,7 +12111,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
       <c r="AI19" s="2" t="inlineStr"/>
       <c r="AJ19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -12233,7 +12233,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
       <c r="AI20" s="2" t="inlineStr"/>
       <c r="AJ20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -12359,7 +12359,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
       <c r="AI21" s="2" t="inlineStr"/>
       <c r="AJ21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -12481,7 +12481,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
       <c r="AI22" s="2" t="inlineStr"/>
       <c r="AJ22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -12607,7 +12607,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
       <c r="AI23" s="2" t="inlineStr"/>
       <c r="AJ23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
       <c r="AI24" s="2" t="inlineStr"/>
       <c r="AJ24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -12855,7 +12855,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
       <c r="AI25" s="2" t="inlineStr"/>
       <c r="AJ25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -12977,7 +12977,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
       <c r="AI26" s="2" t="inlineStr"/>
       <c r="AJ26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -13103,7 +13103,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
       <c r="AI27" s="2" t="inlineStr"/>
       <c r="AJ27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -13225,7 +13225,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
       <c r="AI28" s="2" t="inlineStr"/>
       <c r="AJ28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -13351,7 +13351,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
       <c r="AI29" s="2" t="inlineStr"/>
       <c r="AJ29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -13473,7 +13473,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
       <c r="AI30" s="2" t="inlineStr"/>
       <c r="AJ30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -13599,7 +13599,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
       <c r="AI31" s="2" t="inlineStr"/>
       <c r="AJ31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -13721,7 +13721,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
       <c r="AI32" s="2" t="inlineStr"/>
       <c r="AJ32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
       <c r="AI33" s="2" t="inlineStr"/>
       <c r="AJ33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -13969,7 +13969,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
       <c r="AI34" s="2" t="inlineStr"/>
       <c r="AJ34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -14095,7 +14095,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
       <c r="AI35" s="2" t="inlineStr"/>
       <c r="AJ35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -14217,7 +14217,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
       <c r="AI36" s="2" t="inlineStr"/>
       <c r="AJ36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -14343,7 +14343,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
       <c r="AI37" s="2" t="inlineStr"/>
       <c r="AJ37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -14465,7 +14465,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
       <c r="AI38" s="2" t="inlineStr"/>
       <c r="AJ38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -14591,7 +14591,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
       <c r="AI39" s="2" t="inlineStr"/>
       <c r="AJ39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -14713,7 +14713,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
       <c r="AI40" s="2" t="inlineStr"/>
       <c r="AJ40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -14839,7 +14839,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
       <c r="AI41" s="2" t="inlineStr"/>
       <c r="AJ41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -14961,7 +14961,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
       <c r="AI42" s="2" t="inlineStr"/>
       <c r="AJ42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -15173,7 +15173,7 @@
       <c r="AI43" s="2" t="inlineStr"/>
       <c r="AJ43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
       <c r="AI44" s="2" t="inlineStr"/>
       <c r="AJ44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -15335,7 +15335,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
       <c r="AI45" s="2" t="inlineStr"/>
       <c r="AJ45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
       <c r="AI46" s="2" t="inlineStr"/>
       <c r="AJ46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -15583,7 +15583,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
       <c r="AI47" s="2" t="inlineStr"/>
       <c r="AJ47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -15705,7 +15705,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
       <c r="AI48" s="2" t="inlineStr"/>
       <c r="AJ48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
       <c r="AI49" s="2" t="inlineStr"/>
       <c r="AJ49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -15953,7 +15953,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
       <c r="AI50" s="2" t="inlineStr"/>
       <c r="AJ50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -16079,7 +16079,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
       <c r="AI51" s="2" t="inlineStr"/>
       <c r="AJ51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -16201,7 +16201,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
       <c r="AI52" s="2" t="inlineStr"/>
       <c r="AJ52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -16327,7 +16327,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
       <c r="AI53" s="2" t="inlineStr"/>
       <c r="AJ53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -16449,7 +16449,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
       <c r="AI54" s="2" t="inlineStr"/>
       <c r="AJ54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -16575,7 +16575,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
       <c r="AI55" s="2" t="inlineStr"/>
       <c r="AJ55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -16697,7 +16697,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
       <c r="AI56" s="2" t="inlineStr"/>
       <c r="AJ56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -16823,7 +16823,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
       <c r="AI57" s="2" t="inlineStr"/>
       <c r="AJ57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -16945,7 +16945,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
       <c r="AI58" s="2" t="inlineStr"/>
       <c r="AJ58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -17071,7 +17071,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
       <c r="AI59" s="2" t="inlineStr"/>
       <c r="AJ59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -17193,7 +17193,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
       <c r="AI60" s="2" t="inlineStr"/>
       <c r="AJ60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -17319,7 +17319,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
       <c r="AI61" s="2" t="inlineStr"/>
       <c r="AJ61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -17441,7 +17441,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
       <c r="AI62" s="2" t="inlineStr"/>
       <c r="AJ62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -17567,7 +17567,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
       <c r="AI63" s="2" t="inlineStr"/>
       <c r="AJ63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -17689,7 +17689,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
       <c r="AI64" s="2" t="inlineStr"/>
       <c r="AJ64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -17815,7 +17815,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
       <c r="AI65" s="2" t="inlineStr"/>
       <c r="AJ65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -17937,7 +17937,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
       <c r="AI66" s="2" t="inlineStr"/>
       <c r="AJ66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -18063,7 +18063,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
       <c r="AI67" s="2" t="inlineStr"/>
       <c r="AJ67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -18185,7 +18185,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
       <c r="AI68" s="2" t="inlineStr"/>
       <c r="AJ68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -18311,7 +18311,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
       <c r="AI69" s="2" t="inlineStr"/>
       <c r="AJ69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -18433,7 +18433,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
       <c r="AI70" s="2" t="inlineStr"/>
       <c r="AJ70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -18559,7 +18559,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -18645,7 +18645,7 @@
       <c r="AI71" s="2" t="inlineStr"/>
       <c r="AJ71" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -18681,7 +18681,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
       <c r="AI72" s="2" t="inlineStr"/>
       <c r="AJ72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -18807,7 +18807,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
       <c r="AI73" s="2" t="inlineStr"/>
       <c r="AJ73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -18929,7 +18929,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -19019,7 +19019,7 @@
       <c r="AI74" s="2" t="inlineStr"/>
       <c r="AJ74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -19055,7 +19055,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
       <c r="AI75" s="2" t="inlineStr"/>
       <c r="AJ75" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -19177,7 +19177,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
       <c r="AI76" s="2" t="inlineStr"/>
       <c r="AJ76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -19303,7 +19303,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
       <c r="AI77" s="2" t="inlineStr"/>
       <c r="AJ77" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -19425,7 +19425,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
       <c r="AI78" s="2" t="inlineStr"/>
       <c r="AJ78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -19551,7 +19551,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
       <c r="AI79" s="2" t="inlineStr"/>
       <c r="AJ79" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -19673,7 +19673,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -19763,7 +19763,7 @@
       <c r="AI80" s="2" t="inlineStr"/>
       <c r="AJ80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -19799,7 +19799,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
       <c r="AI81" s="2" t="inlineStr"/>
       <c r="AJ81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -19921,7 +19921,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
       <c r="AI82" s="2" t="inlineStr"/>
       <c r="AJ82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20047,7 +20047,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
       <c r="AI83" s="2" t="inlineStr"/>
       <c r="AJ83" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20169,7 +20169,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
       <c r="AI84" s="2" t="inlineStr"/>
       <c r="AJ84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20295,7 +20295,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
       <c r="AI85" s="2" t="inlineStr"/>
       <c r="AJ85" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20417,7 +20417,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
       <c r="AI86" s="2" t="inlineStr"/>
       <c r="AJ86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20543,7 +20543,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
       <c r="AI87" s="2" t="inlineStr"/>
       <c r="AJ87" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20665,7 +20665,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -20755,7 +20755,7 @@
       <c r="AI88" s="2" t="inlineStr"/>
       <c r="AJ88" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20791,7 +20791,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
       <c r="AI89" s="2" t="inlineStr"/>
       <c r="AJ89" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20913,7 +20913,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
       <c r="AI90" s="2" t="inlineStr"/>
       <c r="AJ90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -21039,7 +21039,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
       <c r="AI91" s="2" t="inlineStr"/>
       <c r="AJ91" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -21161,7 +21161,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
       <c r="AI92" s="2" t="inlineStr"/>
       <c r="AJ92" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -21287,7 +21287,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
       <c r="AI93" s="2" t="inlineStr"/>
       <c r="AJ93" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -21409,7 +21409,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
       <c r="AI94" s="2" t="inlineStr"/>
       <c r="AJ94" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -21535,7 +21535,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
       <c r="AI95" s="2" t="inlineStr"/>
       <c r="AJ95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -21657,7 +21657,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
       <c r="AI96" s="2" t="inlineStr"/>
       <c r="AJ96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -21783,7 +21783,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -21869,7 +21869,7 @@
       <c r="AI97" s="2" t="inlineStr"/>
       <c r="AJ97" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -21905,7 +21905,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
       <c r="AI98" s="2" t="inlineStr"/>
       <c r="AJ98" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -22031,7 +22031,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
       <c r="AI99" s="2" t="inlineStr"/>
       <c r="AJ99" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -22153,7 +22153,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
       <c r="AI100" s="2" t="inlineStr"/>
       <c r="AJ100" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -22279,7 +22279,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
       <c r="AI101" s="2" t="inlineStr"/>
       <c r="AJ101" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -22401,7 +22401,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -22491,7 +22491,7 @@
       <c r="AI102" s="2" t="inlineStr"/>
       <c r="AJ102" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -22527,7 +22527,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
       <c r="AI103" s="2" t="inlineStr"/>
       <c r="AJ103" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -22649,7 +22649,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
       <c r="AI104" s="2" t="inlineStr"/>
       <c r="AJ104" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -22775,7 +22775,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
       <c r="AI105" s="2" t="inlineStr"/>
       <c r="AJ105" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -22897,7 +22897,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
       <c r="AI106" s="2" t="inlineStr"/>
       <c r="AJ106" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -23023,7 +23023,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
       <c r="AI107" s="2" t="inlineStr"/>
       <c r="AJ107" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -23145,7 +23145,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -23235,7 +23235,7 @@
       <c r="AI108" s="2" t="inlineStr"/>
       <c r="AJ108" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -23271,7 +23271,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
       <c r="AI109" s="2" t="inlineStr"/>
       <c r="AJ109" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -23393,7 +23393,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
       <c r="AI110" s="2" t="inlineStr"/>
       <c r="AJ110" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -23519,7 +23519,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -23605,7 +23605,7 @@
       <c r="AI111" s="2" t="inlineStr"/>
       <c r="AJ111" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -23641,7 +23641,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
       <c r="AI112" s="2" t="inlineStr"/>
       <c r="AJ112" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -23767,7 +23767,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
       <c r="AI113" s="2" t="inlineStr"/>
       <c r="AJ113" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -23889,7 +23889,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
       <c r="AI114" s="2" t="inlineStr"/>
       <c r="AJ114" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -24015,7 +24015,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
       <c r="AI115" s="2" t="inlineStr"/>
       <c r="AJ115" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -24137,7 +24137,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
       <c r="AI116" s="2" t="inlineStr"/>
       <c r="AJ116" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -24263,7 +24263,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
       <c r="AI117" s="2" t="inlineStr"/>
       <c r="AJ117" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -24385,7 +24385,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
       <c r="AI118" s="2" t="inlineStr"/>
       <c r="AJ118" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -24511,7 +24511,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -24597,7 +24597,7 @@
       <c r="AI119" s="2" t="inlineStr"/>
       <c r="AJ119" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -24723,7 +24723,7 @@
       <c r="AI120" s="2" t="inlineStr"/>
       <c r="AJ120" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -24759,7 +24759,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
       <c r="AI121" s="2" t="inlineStr"/>
       <c r="AJ121" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -24881,7 +24881,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -24975,7 +24975,7 @@
       </c>
       <c r="AJ122" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -25011,7 +25011,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
       </c>
       <c r="AJ123" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -25137,7 +25137,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
       </c>
       <c r="AJ124" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -25267,7 +25267,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
       </c>
       <c r="AJ125" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -25393,7 +25393,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
       </c>
       <c r="AJ126" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -25523,7 +25523,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
       </c>
       <c r="AJ127" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -25649,7 +25649,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="AJ128" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -25779,7 +25779,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
       </c>
       <c r="AJ129" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -25905,7 +25905,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
       </c>
       <c r="AJ130" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -26035,7 +26035,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
       </c>
       <c r="AJ131" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -26161,7 +26161,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
       </c>
       <c r="AJ132" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
       </c>
       <c r="AJ133" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -26417,7 +26417,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
       <c r="AI134" s="2" t="inlineStr"/>
       <c r="AJ134" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -26543,7 +26543,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
       <c r="AI135" s="2" t="inlineStr"/>
       <c r="AJ135" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -26665,7 +26665,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
       <c r="AI136" s="2" t="inlineStr"/>
       <c r="AJ136" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -26791,7 +26791,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
       <c r="AI137" s="2" t="inlineStr"/>
       <c r="AJ137" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -26913,7 +26913,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
       <c r="AI138" s="2" t="inlineStr"/>
       <c r="AJ138" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
       <c r="AI139" s="2" t="inlineStr"/>
       <c r="AJ139" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -27161,7 +27161,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
       <c r="AI140" s="2" t="inlineStr"/>
       <c r="AJ140" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -27287,7 +27287,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -27373,7 +27373,7 @@
       <c r="AI141" s="2" t="inlineStr"/>
       <c r="AJ141" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -27409,7 +27409,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
       <c r="AI142" s="2" t="inlineStr"/>
       <c r="AJ142" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -27535,7 +27535,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
       <c r="AI143" s="2" t="inlineStr"/>
       <c r="AJ143" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -27657,7 +27657,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
       <c r="AI144" s="2" t="inlineStr"/>
       <c r="AJ144" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -27783,7 +27783,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
       <c r="AI145" s="2" t="inlineStr"/>
       <c r="AJ145" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -27995,7 +27995,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
